--- a/output/Data and Chart Outputs/france_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/france_power_capacity_monthly.xlsx
@@ -352,7 +352,7 @@
           </tx>
           <spPr>
             <a:solidFill>
-              <a:srgbClr val="8A9A2B"/>
+              <a:srgbClr val="9A9A9A"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -367,34 +367,6 @@
           <val>
             <numRef>
               <f>'Chart'!$H$2:$H$69</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="7"/>
-          <order val="7"/>
-          <tx>
-            <strRef>
-              <f>'Chart'!I1</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:solidFill>
-              <a:srgbClr val="9A9A9A"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <cat>
-            <numRef>
-              <f>'Chart'!$A$2:$A$69</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'Chart'!$I$2:$I$69</f>
             </numRef>
           </val>
         </ser>
@@ -650,7 +622,7 @@
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>10</col>
+      <col>9</col>
       <colOff>0</colOff>
       <row>1</row>
       <rowOff>0</rowOff>
@@ -1133,17 +1105,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>2026-10-12 04:52 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Registre national des installations de production et de stockage d'électricité (au 31/07/2026); processed 2026-09-10T14:01:40+00:00</t>
+          <t>Registre national des installations de production et de stockage d'électricité (au 31/07/2026); processed 2026-09-10T14:01:40+00:00; rules v2</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44694e2fd77b5078930c8c3b43604f50e26250f4c344dc475ccf91ac39ac7c8b</t>
+          <t>03dc155484b2e99c0cb61ae23b596bf0c965139dc49f7730164d93a649a18e22</t>
         </is>
       </c>
     </row>
@@ -1155,17 +1127,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 04:47 UTC</t>
+          <t>2026-10-12 04:52 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>solar media 9714 (tableau-de-bord-solaire-photovoltaique-deuxieme-trimestre-2026); wind media 9715 (tableau-de-bord-eolien-deuxieme-trimestre-2026)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>fd65afade8eb6efc8a81fac9c92c263727c89b824d3ae0fd2503368b7abae212e5c0dc62256d396328640ecea5907a1ec4e33c411cd9647f4288ab9160fe027a</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1147,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I69"/>
+  <dimension ref="A1:H69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1224,11 +1191,6 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Bioenergy</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
           <t>Other</t>
         </is>
       </c>
@@ -1256,10 +1218,7 @@
         <v>5.0599</v>
       </c>
       <c r="H2" t="n">
-        <v>2.8822</v>
-      </c>
-      <c r="I2" t="n">
-        <v>7.3986</v>
+        <v>7.4529</v>
       </c>
     </row>
     <row r="3">
@@ -1285,10 +1244,7 @@
         <v>5.0599</v>
       </c>
       <c r="H3" t="n">
-        <v>2.9389</v>
-      </c>
-      <c r="I3" t="n">
-        <v>7.4396</v>
+        <v>7.5415</v>
       </c>
     </row>
     <row r="4">
@@ -1314,10 +1270,7 @@
         <v>5.0599</v>
       </c>
       <c r="H4" t="n">
-        <v>2.9493</v>
-      </c>
-      <c r="I4" t="n">
-        <v>7.4396</v>
+        <v>7.5449</v>
       </c>
     </row>
     <row r="5">
@@ -1343,10 +1296,7 @@
         <v>5.0599</v>
       </c>
       <c r="H5" t="n">
-        <v>2.9516</v>
-      </c>
-      <c r="I5" t="n">
-        <v>7.4397</v>
+        <v>7.5472</v>
       </c>
     </row>
     <row r="6">
@@ -1372,10 +1322,7 @@
         <v>5.0599</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9589</v>
-      </c>
-      <c r="I6" t="n">
-        <v>7.4397</v>
+        <v>7.5545</v>
       </c>
     </row>
     <row r="7">
@@ -1401,10 +1348,7 @@
         <v>5.0599</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9602</v>
-      </c>
-      <c r="I7" t="n">
-        <v>7.440700000000001</v>
+        <v>7.556800000000001</v>
       </c>
     </row>
     <row r="8">
@@ -1430,10 +1374,7 @@
         <v>5.0599</v>
       </c>
       <c r="H8" t="n">
-        <v>2.9634</v>
-      </c>
-      <c r="I8" t="n">
-        <v>7.4411</v>
+        <v>7.5587</v>
       </c>
     </row>
     <row r="9">
@@ -1459,10 +1400,7 @@
         <v>5.0599</v>
       </c>
       <c r="H9" t="n">
-        <v>2.9649</v>
-      </c>
-      <c r="I9" t="n">
-        <v>7.4939</v>
+        <v>7.613</v>
       </c>
     </row>
     <row r="10">
@@ -1488,10 +1426,7 @@
         <v>5.0599</v>
       </c>
       <c r="H10" t="n">
-        <v>2.9975</v>
-      </c>
-      <c r="I10" t="n">
-        <v>7.5108</v>
+        <v>7.6625</v>
       </c>
     </row>
     <row r="11">
@@ -1517,10 +1452,7 @@
         <v>5.0599</v>
       </c>
       <c r="H11" t="n">
-        <v>3</v>
-      </c>
-      <c r="I11" t="n">
-        <v>7.5317</v>
+        <v>7.686</v>
       </c>
     </row>
     <row r="12">
@@ -1546,10 +1478,7 @@
         <v>5.0599</v>
       </c>
       <c r="H12" t="n">
-        <v>3.0005</v>
-      </c>
-      <c r="I12" t="n">
-        <v>7.5863</v>
+        <v>7.741000000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1575,10 +1504,7 @@
         <v>5.0599</v>
       </c>
       <c r="H13" t="n">
-        <v>3.0124</v>
-      </c>
-      <c r="I13" t="n">
-        <v>7.625</v>
+        <v>7.7829</v>
       </c>
     </row>
     <row r="14">
@@ -1604,10 +1530,7 @@
         <v>5.0599</v>
       </c>
       <c r="H14" t="n">
-        <v>3.0175</v>
-      </c>
-      <c r="I14" t="n">
-        <v>7.6481</v>
+        <v>7.811100000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1633,10 +1556,7 @@
         <v>5.0599</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0183</v>
-      </c>
-      <c r="I15" t="n">
-        <v>7.6611</v>
+        <v>7.8249</v>
       </c>
     </row>
     <row r="16">
@@ -1662,10 +1582,7 @@
         <v>5.0599</v>
       </c>
       <c r="H16" t="n">
-        <v>3.0192</v>
-      </c>
-      <c r="I16" t="n">
-        <v>7.6689</v>
+        <v>7.833600000000001</v>
       </c>
     </row>
     <row r="17">
@@ -1691,10 +1608,7 @@
         <v>5.0599</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0207</v>
-      </c>
-      <c r="I17" t="n">
-        <v>7.694500000000001</v>
+        <v>7.8607</v>
       </c>
     </row>
     <row r="18">
@@ -1720,10 +1634,7 @@
         <v>5.0599</v>
       </c>
       <c r="H18" t="n">
-        <v>3.0322</v>
-      </c>
-      <c r="I18" t="n">
-        <v>7.727600000000001</v>
+        <v>7.881</v>
       </c>
     </row>
     <row r="19">
@@ -1749,10 +1660,7 @@
         <v>5.0599</v>
       </c>
       <c r="H19" t="n">
-        <v>3.0379</v>
-      </c>
-      <c r="I19" t="n">
-        <v>7.737</v>
+        <v>7.8961</v>
       </c>
     </row>
     <row r="20">
@@ -1778,10 +1686,7 @@
         <v>5.0599</v>
       </c>
       <c r="H20" t="n">
-        <v>3.0395</v>
-      </c>
-      <c r="I20" t="n">
-        <v>7.7587</v>
+        <v>7.9194</v>
       </c>
     </row>
     <row r="21">
@@ -1807,10 +1712,7 @@
         <v>5.0599</v>
       </c>
       <c r="H21" t="n">
-        <v>3.0548</v>
-      </c>
-      <c r="I21" t="n">
-        <v>7.79</v>
+        <v>7.966000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -1836,10 +1738,7 @@
         <v>5.0599</v>
       </c>
       <c r="H22" t="n">
-        <v>3.0565</v>
-      </c>
-      <c r="I22" t="n">
-        <v>7.825900000000001</v>
+        <v>7.979500000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1865,10 +1764,7 @@
         <v>5.0599</v>
       </c>
       <c r="H23" t="n">
-        <v>3.0603</v>
-      </c>
-      <c r="I23" t="n">
-        <v>7.8448</v>
+        <v>8.0022</v>
       </c>
     </row>
     <row r="24">
@@ -1894,10 +1790,7 @@
         <v>5.0599</v>
       </c>
       <c r="H24" t="n">
-        <v>3.075</v>
-      </c>
-      <c r="I24" t="n">
-        <v>7.8587</v>
+        <v>8.0175</v>
       </c>
     </row>
     <row r="25">
@@ -1923,10 +1816,7 @@
         <v>5.0599</v>
       </c>
       <c r="H25" t="n">
-        <v>3.076</v>
-      </c>
-      <c r="I25" t="n">
-        <v>7.8732</v>
+        <v>8.0329</v>
       </c>
     </row>
     <row r="26">
@@ -1952,10 +1842,7 @@
         <v>5.0599</v>
       </c>
       <c r="H26" t="n">
-        <v>3.0786</v>
-      </c>
-      <c r="I26" t="n">
-        <v>7.9182</v>
+        <v>8.080500000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1981,10 +1868,7 @@
         <v>5.0599</v>
       </c>
       <c r="H27" t="n">
-        <v>3.0803</v>
-      </c>
-      <c r="I27" t="n">
-        <v>7.933199999999999</v>
+        <v>8.088200000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2010,10 +1894,7 @@
         <v>5.0599</v>
       </c>
       <c r="H28" t="n">
-        <v>3.0827</v>
-      </c>
-      <c r="I28" t="n">
-        <v>7.9544</v>
+        <v>8.1119</v>
       </c>
     </row>
     <row r="29">
@@ -2039,10 +1920,7 @@
         <v>5.0599</v>
       </c>
       <c r="H29" t="n">
-        <v>3.0853</v>
-      </c>
-      <c r="I29" t="n">
-        <v>7.969099999999999</v>
+        <v>8.129099999999999</v>
       </c>
     </row>
     <row r="30">
@@ -2068,10 +1946,7 @@
         <v>5.0603</v>
       </c>
       <c r="H30" t="n">
-        <v>3.0865</v>
-      </c>
-      <c r="I30" t="n">
-        <v>8.140700000000001</v>
+        <v>8.302</v>
       </c>
     </row>
     <row r="31">
@@ -2097,10 +1972,7 @@
         <v>5.0603</v>
       </c>
       <c r="H31" t="n">
-        <v>3.1088</v>
-      </c>
-      <c r="I31" t="n">
-        <v>8.151</v>
+        <v>8.313499999999999</v>
       </c>
     </row>
     <row r="32">
@@ -2126,10 +1998,7 @@
         <v>5.0603</v>
       </c>
       <c r="H32" t="n">
-        <v>3.1113</v>
-      </c>
-      <c r="I32" t="n">
-        <v>8.1714</v>
+        <v>8.335900000000001</v>
       </c>
     </row>
     <row r="33">
@@ -2155,10 +2024,7 @@
         <v>5.0603</v>
       </c>
       <c r="H33" t="n">
-        <v>3.1121</v>
-      </c>
-      <c r="I33" t="n">
-        <v>8.1989</v>
+        <v>8.360799999999999</v>
       </c>
     </row>
     <row r="34">
@@ -2184,10 +2050,7 @@
         <v>5.0603</v>
       </c>
       <c r="H34" t="n">
-        <v>3.1169</v>
-      </c>
-      <c r="I34" t="n">
-        <v>8.2225</v>
+        <v>8.3889</v>
       </c>
     </row>
     <row r="35">
@@ -2213,10 +2076,7 @@
         <v>5.0603</v>
       </c>
       <c r="H35" t="n">
-        <v>3.1183</v>
-      </c>
-      <c r="I35" t="n">
-        <v>8.254599999999998</v>
+        <v>8.421899999999999</v>
       </c>
     </row>
     <row r="36">
@@ -2242,10 +2102,7 @@
         <v>5.0603</v>
       </c>
       <c r="H36" t="n">
-        <v>3.1183</v>
-      </c>
-      <c r="I36" t="n">
-        <v>8.270199999999999</v>
+        <v>8.4375</v>
       </c>
     </row>
     <row r="37">
@@ -2271,10 +2128,7 @@
         <v>5.0603</v>
       </c>
       <c r="H37" t="n">
-        <v>3.1311</v>
-      </c>
-      <c r="I37" t="n">
-        <v>8.279299999999999</v>
+        <v>8.455399999999999</v>
       </c>
     </row>
     <row r="38">
@@ -2300,10 +2154,7 @@
         <v>5.0603</v>
       </c>
       <c r="H38" t="n">
-        <v>3.132</v>
-      </c>
-      <c r="I38" t="n">
-        <v>8.297299999999998</v>
+        <v>8.474299999999999</v>
       </c>
     </row>
     <row r="39">
@@ -2329,10 +2180,7 @@
         <v>5.0603</v>
       </c>
       <c r="H39" t="n">
-        <v>3.1328</v>
-      </c>
-      <c r="I39" t="n">
-        <v>8.347199999999999</v>
+        <v>8.487199999999998</v>
       </c>
     </row>
     <row r="40">
@@ -2358,10 +2206,7 @@
         <v>5.0603</v>
       </c>
       <c r="H40" t="n">
-        <v>3.1345</v>
-      </c>
-      <c r="I40" t="n">
-        <v>8.365399999999999</v>
+        <v>8.507</v>
       </c>
     </row>
     <row r="41">
@@ -2387,10 +2232,7 @@
         <v>5.0603</v>
       </c>
       <c r="H41" t="n">
-        <v>3.137</v>
-      </c>
-      <c r="I41" t="n">
-        <v>8.399600000000001</v>
+        <v>8.543699999999999</v>
       </c>
     </row>
     <row r="42">
@@ -2416,10 +2258,7 @@
         <v>5.0603</v>
       </c>
       <c r="H42" t="n">
-        <v>3.137</v>
-      </c>
-      <c r="I42" t="n">
-        <v>8.413</v>
+        <v>8.5571</v>
       </c>
     </row>
     <row r="43">
@@ -2445,10 +2284,7 @@
         <v>5.0603</v>
       </c>
       <c r="H43" t="n">
-        <v>3.138</v>
-      </c>
-      <c r="I43" t="n">
-        <v>8.4267</v>
+        <v>8.5718</v>
       </c>
     </row>
     <row r="44">
@@ -2474,10 +2310,7 @@
         <v>5.0604</v>
       </c>
       <c r="H44" t="n">
-        <v>3.1381</v>
-      </c>
-      <c r="I44" t="n">
-        <v>8.4533</v>
+        <v>8.597099999999999</v>
       </c>
     </row>
     <row r="45">
@@ -2503,10 +2336,7 @@
         <v>5.0604</v>
       </c>
       <c r="H45" t="n">
-        <v>3.1381</v>
-      </c>
-      <c r="I45" t="n">
-        <v>8.5152</v>
+        <v>8.659000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -2532,10 +2362,7 @@
         <v>5.0604</v>
       </c>
       <c r="H46" t="n">
-        <v>3.1386</v>
-      </c>
-      <c r="I46" t="n">
-        <v>8.533000000000001</v>
+        <v>8.667</v>
       </c>
     </row>
     <row r="47">
@@ -2561,10 +2388,7 @@
         <v>5.0604</v>
       </c>
       <c r="H47" t="n">
-        <v>3.1386</v>
-      </c>
-      <c r="I47" t="n">
-        <v>8.536799999999999</v>
+        <v>8.6708</v>
       </c>
     </row>
     <row r="48">
@@ -2590,10 +2414,7 @@
         <v>5.0604</v>
       </c>
       <c r="H48" t="n">
-        <v>3.1587</v>
-      </c>
-      <c r="I48" t="n">
-        <v>8.558999999999999</v>
+        <v>8.6906</v>
       </c>
     </row>
     <row r="49">
@@ -2619,10 +2440,7 @@
         <v>5.0604</v>
       </c>
       <c r="H49" t="n">
-        <v>3.1599</v>
-      </c>
-      <c r="I49" t="n">
-        <v>8.5869</v>
+        <v>8.7058</v>
       </c>
     </row>
     <row r="50">
@@ -2648,10 +2466,7 @@
         <v>5.0604</v>
       </c>
       <c r="H50" t="n">
-        <v>3.1602</v>
-      </c>
-      <c r="I50" t="n">
-        <v>8.6036</v>
+        <v>8.722799999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2677,10 +2492,7 @@
         <v>5.0604</v>
       </c>
       <c r="H51" t="n">
-        <v>3.1608</v>
-      </c>
-      <c r="I51" t="n">
-        <v>8.630000000000001</v>
+        <v>8.7255</v>
       </c>
     </row>
     <row r="52">
@@ -2706,10 +2518,7 @@
         <v>5.0604</v>
       </c>
       <c r="H52" t="n">
-        <v>3.1611</v>
-      </c>
-      <c r="I52" t="n">
-        <v>8.631</v>
+        <v>8.726800000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2735,10 +2544,7 @@
         <v>5.0604</v>
       </c>
       <c r="H53" t="n">
-        <v>3.1627</v>
-      </c>
-      <c r="I53" t="n">
-        <v>8.6334</v>
+        <v>8.7302</v>
       </c>
     </row>
     <row r="54">
@@ -2764,10 +2570,7 @@
         <v>5.0604</v>
       </c>
       <c r="H54" t="n">
-        <v>3.1627</v>
-      </c>
-      <c r="I54" t="n">
-        <v>8.654999999999999</v>
+        <v>8.751799999999999</v>
       </c>
     </row>
     <row r="55">
@@ -2793,10 +2596,7 @@
         <v>5.0604</v>
       </c>
       <c r="H55" t="n">
-        <v>3.1628</v>
-      </c>
-      <c r="I55" t="n">
-        <v>8.680899999999999</v>
+        <v>8.777799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -2822,10 +2622,7 @@
         <v>5.0604</v>
       </c>
       <c r="H56" t="n">
-        <v>3.1839</v>
-      </c>
-      <c r="I56" t="n">
-        <v>8.711399999999999</v>
+        <v>8.8294</v>
       </c>
     </row>
     <row r="57">
@@ -2851,10 +2648,7 @@
         <v>5.0604</v>
       </c>
       <c r="H57" t="n">
-        <v>3.1846</v>
-      </c>
-      <c r="I57" t="n">
-        <v>8.816099999999999</v>
+        <v>8.934799999999999</v>
       </c>
     </row>
     <row r="58">
@@ -2880,10 +2674,7 @@
         <v>5.0604</v>
       </c>
       <c r="H58" t="n">
-        <v>3.1846</v>
-      </c>
-      <c r="I58" t="n">
-        <v>8.835699999999999</v>
+        <v>8.9544</v>
       </c>
     </row>
     <row r="59">
@@ -2909,10 +2700,7 @@
         <v>5.0604</v>
       </c>
       <c r="H59" t="n">
-        <v>3.1847</v>
-      </c>
-      <c r="I59" t="n">
-        <v>8.856399999999999</v>
+        <v>8.975199999999999</v>
       </c>
     </row>
     <row r="60">
@@ -2938,10 +2726,7 @@
         <v>5.0604</v>
       </c>
       <c r="H60" t="n">
-        <v>3.1863</v>
-      </c>
-      <c r="I60" t="n">
-        <v>8.8954</v>
+        <v>9.015799999999999</v>
       </c>
     </row>
     <row r="61">
@@ -2967,10 +2752,7 @@
         <v>5.0604</v>
       </c>
       <c r="H61" t="n">
-        <v>3.1865</v>
-      </c>
-      <c r="I61" t="n">
-        <v>9.043199999999999</v>
+        <v>9.158899999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2996,10 +2778,7 @@
         <v>5.0604</v>
       </c>
       <c r="H62" t="n">
-        <v>3.1977</v>
-      </c>
-      <c r="I62" t="n">
-        <v>9.1235</v>
+        <v>9.2456</v>
       </c>
     </row>
     <row r="63">
@@ -3025,10 +2804,7 @@
         <v>5.0604</v>
       </c>
       <c r="H63" t="n">
-        <v>3.1977</v>
-      </c>
-      <c r="I63" t="n">
-        <v>9.408299999999999</v>
+        <v>9.5304</v>
       </c>
     </row>
     <row r="64">
@@ -3054,10 +2830,7 @@
         <v>5.0604</v>
       </c>
       <c r="H64" t="n">
-        <v>3.1986</v>
-      </c>
-      <c r="I64" t="n">
-        <v>9.449999999999999</v>
+        <v>9.573</v>
       </c>
     </row>
     <row r="65">
@@ -3083,10 +2856,7 @@
         <v>5.0604</v>
       </c>
       <c r="H65" t="n">
-        <v>3.2034</v>
-      </c>
-      <c r="I65" t="n">
-        <v>9.579000000000001</v>
+        <v>9.7012</v>
       </c>
     </row>
     <row r="66">
@@ -3112,10 +2882,7 @@
         <v>5.0604</v>
       </c>
       <c r="H66" t="n">
-        <v>3.2039</v>
-      </c>
-      <c r="I66" t="n">
-        <v>9.6601</v>
+        <v>9.7828</v>
       </c>
     </row>
     <row r="67">
@@ -3141,10 +2908,7 @@
         <v>5.0604</v>
       </c>
       <c r="H67" t="n">
-        <v>3.2067</v>
-      </c>
-      <c r="I67" t="n">
-        <v>9.6715</v>
+        <v>9.7942</v>
       </c>
     </row>
     <row r="68">
@@ -3170,10 +2934,7 @@
         <v>5.0604</v>
       </c>
       <c r="H68" t="n">
-        <v>3.2068</v>
-      </c>
-      <c r="I68" t="n">
-        <v>9.719100000000001</v>
+        <v>9.841799999999999</v>
       </c>
     </row>
     <row r="69">
@@ -3199,10 +2960,7 @@
         <v>5.0604</v>
       </c>
       <c r="H69" t="n">
-        <v>3.2068</v>
-      </c>
-      <c r="I69" t="n">
-        <v>9.745999999999999</v>
+        <v>9.8687</v>
       </c>
     </row>
   </sheetData>
@@ -4105,10 +3863,10 @@
         <v>2654.4</v>
       </c>
       <c r="I2" t="n">
-        <v>2882.2</v>
+        <v>1888</v>
       </c>
       <c r="J2" t="n">
-        <v>1833.7</v>
+        <v>2827.9</v>
       </c>
       <c r="K2" t="n">
         <v>133021.8</v>
@@ -4158,10 +3916,10 @@
         <v>2657.6</v>
       </c>
       <c r="I3" t="n">
-        <v>2938.9</v>
+        <v>1935.6</v>
       </c>
       <c r="J3" t="n">
-        <v>1833.7</v>
+        <v>2836.9</v>
       </c>
       <c r="K3" t="n">
         <v>133365</v>
@@ -4211,10 +3969,10 @@
         <v>2657.6</v>
       </c>
       <c r="I4" t="n">
-        <v>2949.3</v>
+        <v>1939</v>
       </c>
       <c r="J4" t="n">
-        <v>1833.7</v>
+        <v>2844</v>
       </c>
       <c r="K4" t="n">
         <v>133793.5</v>
@@ -4264,10 +4022,10 @@
         <v>2657.6</v>
       </c>
       <c r="I5" t="n">
-        <v>2951.6</v>
+        <v>1941.3</v>
       </c>
       <c r="J5" t="n">
-        <v>1833.8</v>
+        <v>2844.1</v>
       </c>
       <c r="K5" t="n">
         <v>134192</v>
@@ -4317,10 +4075,10 @@
         <v>2657.6</v>
       </c>
       <c r="I6" t="n">
-        <v>2958.9</v>
+        <v>1948.6</v>
       </c>
       <c r="J6" t="n">
-        <v>1833.8</v>
+        <v>2844.1</v>
       </c>
       <c r="K6" t="n">
         <v>134663.6</v>
@@ -4370,10 +4128,10 @@
         <v>2658.6</v>
       </c>
       <c r="I7" t="n">
-        <v>2960.2</v>
+        <v>1949.9</v>
       </c>
       <c r="J7" t="n">
-        <v>1833.8</v>
+        <v>2844.1</v>
       </c>
       <c r="K7" t="n">
         <v>134971.2</v>
@@ -4423,10 +4181,10 @@
         <v>2658.6</v>
       </c>
       <c r="I8" t="n">
-        <v>2963.4</v>
+        <v>1951.8</v>
       </c>
       <c r="J8" t="n">
-        <v>1834.2</v>
+        <v>2845.8</v>
       </c>
       <c r="K8" t="n">
         <v>135690.3</v>
@@ -4476,10 +4234,10 @@
         <v>2658.6</v>
       </c>
       <c r="I9" t="n">
-        <v>2964.9</v>
+        <v>1953.3</v>
       </c>
       <c r="J9" t="n">
-        <v>1834.2</v>
+        <v>2845.8</v>
       </c>
       <c r="K9" t="n">
         <v>136094.5</v>
@@ -4529,10 +4287,10 @@
         <v>2658.6</v>
       </c>
       <c r="I10" t="n">
-        <v>2997.5</v>
+        <v>1985.9</v>
       </c>
       <c r="J10" t="n">
-        <v>1834.2</v>
+        <v>2845.8</v>
       </c>
       <c r="K10" t="n">
         <v>136351.4</v>
@@ -4582,10 +4340,10 @@
         <v>2658.6</v>
       </c>
       <c r="I11" t="n">
-        <v>3000</v>
+        <v>1988.5</v>
       </c>
       <c r="J11" t="n">
-        <v>1834.2</v>
+        <v>2845.8</v>
       </c>
       <c r="K11" t="n">
         <v>136615.2</v>
@@ -4635,10 +4393,10 @@
         <v>2658.6</v>
       </c>
       <c r="I12" t="n">
-        <v>3000.5</v>
+        <v>1988.9</v>
       </c>
       <c r="J12" t="n">
-        <v>1834.2</v>
+        <v>2845.8</v>
       </c>
       <c r="K12" t="n">
         <v>137073.2</v>
@@ -4688,10 +4446,10 @@
         <v>2658.6</v>
       </c>
       <c r="I13" t="n">
-        <v>3012.4</v>
+        <v>1992.1</v>
       </c>
       <c r="J13" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="K13" t="n">
         <v>137488.4</v>
@@ -4741,10 +4499,10 @@
         <v>2658.6</v>
       </c>
       <c r="I14" t="n">
-        <v>3017.5</v>
+        <v>1997.2</v>
       </c>
       <c r="J14" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="K14" t="n">
         <v>137892.1</v>
@@ -4794,10 +4552,10 @@
         <v>2659.3</v>
       </c>
       <c r="I15" t="n">
-        <v>3018.3</v>
+        <v>1998</v>
       </c>
       <c r="J15" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="K15" t="n">
         <v>138168.3</v>
@@ -4847,10 +4605,10 @@
         <v>2659.3</v>
       </c>
       <c r="I16" t="n">
-        <v>3019.2</v>
+        <v>1998.9</v>
       </c>
       <c r="J16" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="K16" t="n">
         <v>138490.1</v>
@@ -4900,10 +4658,10 @@
         <v>2659.3</v>
       </c>
       <c r="I17" t="n">
-        <v>3020.7</v>
+        <v>2000.4</v>
       </c>
       <c r="J17" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="K17" t="n">
         <v>138853.9</v>
@@ -4953,10 +4711,10 @@
         <v>2659.3</v>
       </c>
       <c r="I18" t="n">
-        <v>3032.2</v>
+        <v>2011.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1858.5</v>
+        <v>2878.8</v>
       </c>
       <c r="K18" t="n">
         <v>139200.7</v>
@@ -5006,10 +4764,10 @@
         <v>2659.3</v>
       </c>
       <c r="I19" t="n">
-        <v>3037.9</v>
+        <v>2017.6</v>
       </c>
       <c r="J19" t="n">
-        <v>1858.5</v>
+        <v>2878.8</v>
       </c>
       <c r="K19" t="n">
         <v>139508.3</v>
@@ -5059,10 +4817,10 @@
         <v>2659.3</v>
       </c>
       <c r="I20" t="n">
-        <v>3039.5</v>
+        <v>2019.2</v>
       </c>
       <c r="J20" t="n">
-        <v>1858.5</v>
+        <v>2878.8</v>
       </c>
       <c r="K20" t="n">
         <v>140371.2</v>
@@ -5112,10 +4870,10 @@
         <v>2659.3</v>
       </c>
       <c r="I21" t="n">
-        <v>3054.8</v>
+        <v>2034.5</v>
       </c>
       <c r="J21" t="n">
-        <v>1858.5</v>
+        <v>2878.8</v>
       </c>
       <c r="K21" t="n">
         <v>140733.8</v>
@@ -5165,10 +4923,10 @@
         <v>2659.3</v>
       </c>
       <c r="I22" t="n">
-        <v>3056.5</v>
+        <v>2036.1</v>
       </c>
       <c r="J22" t="n">
-        <v>1882.5</v>
+        <v>2902.8</v>
       </c>
       <c r="K22" t="n">
         <v>141000.3</v>
@@ -5218,10 +4976,10 @@
         <v>2659.3</v>
       </c>
       <c r="I23" t="n">
-        <v>3060.3</v>
+        <v>2039.9</v>
       </c>
       <c r="J23" t="n">
-        <v>1882.5</v>
+        <v>2902.8</v>
       </c>
       <c r="K23" t="n">
         <v>141523.8</v>
@@ -5271,10 +5029,10 @@
         <v>2659.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3075</v>
+        <v>2041.3</v>
       </c>
       <c r="J24" t="n">
-        <v>1882.5</v>
+        <v>2916.2</v>
       </c>
       <c r="K24" t="n">
         <v>142021</v>
@@ -5324,10 +5082,10 @@
         <v>2659.3</v>
       </c>
       <c r="I25" t="n">
-        <v>3076</v>
+        <v>2042.3</v>
       </c>
       <c r="J25" t="n">
-        <v>1882.6</v>
+        <v>2916.3</v>
       </c>
       <c r="K25" t="n">
         <v>142388.4</v>
@@ -5377,10 +5135,10 @@
         <v>2659.3</v>
       </c>
       <c r="I26" t="n">
-        <v>3078.6</v>
+        <v>2044.9</v>
       </c>
       <c r="J26" t="n">
-        <v>1882.6</v>
+        <v>2916.3</v>
       </c>
       <c r="K26" t="n">
         <v>142945.6</v>
@@ -5430,10 +5188,10 @@
         <v>2659.3</v>
       </c>
       <c r="I27" t="n">
-        <v>3080.3</v>
+        <v>2045.7</v>
       </c>
       <c r="J27" t="n">
-        <v>1890.7</v>
+        <v>2925.2</v>
       </c>
       <c r="K27" t="n">
         <v>143421.9</v>
@@ -5483,10 +5241,10 @@
         <v>2659.3</v>
       </c>
       <c r="I28" t="n">
-        <v>3082.7</v>
+        <v>2048.2</v>
       </c>
       <c r="J28" t="n">
-        <v>1890.7</v>
+        <v>2925.2</v>
       </c>
       <c r="K28" t="n">
         <v>143750.9</v>
@@ -5536,10 +5294,10 @@
         <v>2659.3</v>
       </c>
       <c r="I29" t="n">
-        <v>3085.3</v>
+        <v>2050.7</v>
       </c>
       <c r="J29" t="n">
-        <v>1890.7</v>
+        <v>2925.2</v>
       </c>
       <c r="K29" t="n">
         <v>144620.5</v>
@@ -5589,10 +5347,10 @@
         <v>2659.3</v>
       </c>
       <c r="I30" t="n">
-        <v>3086.5</v>
+        <v>2052</v>
       </c>
       <c r="J30" t="n">
-        <v>1890.7</v>
+        <v>2925.2</v>
       </c>
       <c r="K30" t="n">
         <v>144894.9</v>
@@ -5642,10 +5400,10 @@
         <v>2659.3</v>
       </c>
       <c r="I31" t="n">
-        <v>3108.8</v>
+        <v>2053.2</v>
       </c>
       <c r="J31" t="n">
-        <v>1890.7</v>
+        <v>2946.2</v>
       </c>
       <c r="K31" t="n">
         <v>145353.6</v>
@@ -5695,10 +5453,10 @@
         <v>2659.3</v>
       </c>
       <c r="I32" t="n">
-        <v>3111.3</v>
+        <v>2055.2</v>
       </c>
       <c r="J32" t="n">
-        <v>1890.7</v>
+        <v>2946.7</v>
       </c>
       <c r="K32" t="n">
         <v>146217.9</v>
@@ -5748,10 +5506,10 @@
         <v>2659.3</v>
       </c>
       <c r="I33" t="n">
-        <v>3112.1</v>
+        <v>2055.7</v>
       </c>
       <c r="J33" t="n">
-        <v>1893.8</v>
+        <v>2950.2</v>
       </c>
       <c r="K33" t="n">
         <v>146705.8</v>
@@ -5801,10 +5559,10 @@
         <v>2664.5</v>
       </c>
       <c r="I34" t="n">
-        <v>3116.9</v>
+        <v>2060.2</v>
       </c>
       <c r="J34" t="n">
-        <v>1893.8</v>
+        <v>2950.5</v>
       </c>
       <c r="K34" t="n">
         <v>147045.7</v>
@@ -5854,10 +5612,10 @@
         <v>2664.5</v>
       </c>
       <c r="I35" t="n">
-        <v>3118.3</v>
+        <v>2061.6</v>
       </c>
       <c r="J35" t="n">
-        <v>1894.3</v>
+        <v>2951</v>
       </c>
       <c r="K35" t="n">
         <v>147390.5</v>
@@ -5907,10 +5665,10 @@
         <v>2664.5</v>
       </c>
       <c r="I36" t="n">
-        <v>3118.3</v>
+        <v>2061.6</v>
       </c>
       <c r="J36" t="n">
-        <v>1894.3</v>
+        <v>2951</v>
       </c>
       <c r="K36" t="n">
         <v>147813.3</v>
@@ -5960,10 +5718,10 @@
         <v>2664.5</v>
       </c>
       <c r="I37" t="n">
-        <v>3131.1</v>
+        <v>2070.4</v>
       </c>
       <c r="J37" t="n">
-        <v>1894.3</v>
+        <v>2955</v>
       </c>
       <c r="K37" t="n">
         <v>148180.7</v>
@@ -6013,10 +5771,10 @@
         <v>2664.5</v>
       </c>
       <c r="I38" t="n">
-        <v>3132</v>
+        <v>2071.3</v>
       </c>
       <c r="J38" t="n">
-        <v>1894.3</v>
+        <v>2955</v>
       </c>
       <c r="K38" t="n">
         <v>148693.3</v>
@@ -6066,10 +5824,10 @@
         <v>2664.5</v>
       </c>
       <c r="I39" t="n">
-        <v>3132.8</v>
+        <v>2072.2</v>
       </c>
       <c r="J39" t="n">
-        <v>1932.2</v>
+        <v>2992.9</v>
       </c>
       <c r="K39" t="n">
         <v>149211.5</v>
@@ -6119,10 +5877,10 @@
         <v>2664.5</v>
       </c>
       <c r="I40" t="n">
-        <v>3134.5</v>
+        <v>2073.8</v>
       </c>
       <c r="J40" t="n">
-        <v>1932.2</v>
+        <v>2992.9</v>
       </c>
       <c r="K40" t="n">
         <v>149713.2</v>
@@ -6172,10 +5930,10 @@
         <v>2672.5</v>
       </c>
       <c r="I41" t="n">
-        <v>3137</v>
+        <v>2076.3</v>
       </c>
       <c r="J41" t="n">
-        <v>1932.2</v>
+        <v>2992.9</v>
       </c>
       <c r="K41" t="n">
         <v>150173.9</v>
@@ -6225,10 +5983,10 @@
         <v>2672.5</v>
       </c>
       <c r="I42" t="n">
-        <v>3137</v>
+        <v>2076.3</v>
       </c>
       <c r="J42" t="n">
-        <v>1932.2</v>
+        <v>2992.9</v>
       </c>
       <c r="K42" t="n">
         <v>150642.2</v>
@@ -6278,10 +6036,10 @@
         <v>2672.5</v>
       </c>
       <c r="I43" t="n">
-        <v>3138</v>
+        <v>2077.3</v>
       </c>
       <c r="J43" t="n">
-        <v>1932.2</v>
+        <v>2992.9</v>
       </c>
       <c r="K43" t="n">
         <v>151114.6</v>
@@ -6331,10 +6089,10 @@
         <v>2672.5</v>
       </c>
       <c r="I44" t="n">
-        <v>3138.1</v>
+        <v>2077.4</v>
       </c>
       <c r="J44" t="n">
-        <v>1933.6</v>
+        <v>2994.2</v>
       </c>
       <c r="K44" t="n">
         <v>151617.5</v>
@@ -6384,10 +6142,10 @@
         <v>2672.5</v>
       </c>
       <c r="I45" t="n">
-        <v>3138.1</v>
+        <v>2077.4</v>
       </c>
       <c r="J45" t="n">
-        <v>1933.6</v>
+        <v>2994.2</v>
       </c>
       <c r="K45" t="n">
         <v>152310.9</v>
@@ -6437,10 +6195,10 @@
         <v>2672.5</v>
       </c>
       <c r="I46" t="n">
-        <v>3138.6</v>
+        <v>2077.9</v>
       </c>
       <c r="J46" t="n">
-        <v>1943.9</v>
+        <v>3004.6</v>
       </c>
       <c r="K46" t="n">
         <v>152750.7</v>
@@ -6490,10 +6248,10 @@
         <v>2672.5</v>
       </c>
       <c r="I47" t="n">
-        <v>3138.6</v>
+        <v>2077.9</v>
       </c>
       <c r="J47" t="n">
-        <v>1943.9</v>
+        <v>3004.6</v>
       </c>
       <c r="K47" t="n">
         <v>153230.2</v>
@@ -6543,10 +6301,10 @@
         <v>2672.5</v>
       </c>
       <c r="I48" t="n">
-        <v>3158.7</v>
+        <v>2078.5</v>
       </c>
       <c r="J48" t="n">
-        <v>1946.9</v>
+        <v>3027.1</v>
       </c>
       <c r="K48" t="n">
         <v>153974.3</v>
@@ -6596,10 +6354,10 @@
         <v>2672.5</v>
       </c>
       <c r="I49" t="n">
-        <v>3159.9</v>
+        <v>2079.8</v>
       </c>
       <c r="J49" t="n">
-        <v>1960.9</v>
+        <v>3041.1</v>
       </c>
       <c r="K49" t="n">
         <v>154575.5</v>
@@ -6649,10 +6407,10 @@
         <v>2672.5</v>
       </c>
       <c r="I50" t="n">
-        <v>3160.2</v>
+        <v>2080.1</v>
       </c>
       <c r="J50" t="n">
-        <v>1960.9</v>
+        <v>3041.1</v>
       </c>
       <c r="K50" t="n">
         <v>156808.7</v>
@@ -6702,10 +6460,10 @@
         <v>2672.5</v>
       </c>
       <c r="I51" t="n">
-        <v>3160.8</v>
+        <v>2080.4</v>
       </c>
       <c r="J51" t="n">
-        <v>1984.9</v>
+        <v>3065.4</v>
       </c>
       <c r="K51" t="n">
         <v>157395</v>
@@ -6755,10 +6513,10 @@
         <v>2673.5</v>
       </c>
       <c r="I52" t="n">
-        <v>3161.1</v>
+        <v>2080.7</v>
       </c>
       <c r="J52" t="n">
-        <v>1984.9</v>
+        <v>3065.4</v>
       </c>
       <c r="K52" t="n">
         <v>157932.2</v>
@@ -6808,10 +6566,10 @@
         <v>2673.5</v>
       </c>
       <c r="I53" t="n">
-        <v>3162.7</v>
+        <v>2081.7</v>
       </c>
       <c r="J53" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K53" t="n">
         <v>158414.8</v>
@@ -6861,10 +6619,10 @@
         <v>2673.5</v>
       </c>
       <c r="I54" t="n">
-        <v>3162.7</v>
+        <v>2081.7</v>
       </c>
       <c r="J54" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K54" t="n">
         <v>158984</v>
@@ -6914,10 +6672,10 @@
         <v>2673.5</v>
       </c>
       <c r="I55" t="n">
-        <v>3162.8</v>
+        <v>2081.8</v>
       </c>
       <c r="J55" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K55" t="n">
         <v>159514.9</v>
@@ -6967,10 +6725,10 @@
         <v>2673.5</v>
       </c>
       <c r="I56" t="n">
-        <v>3183.9</v>
+        <v>2102.9</v>
       </c>
       <c r="J56" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K56" t="n">
         <v>160090.8</v>
@@ -7020,10 +6778,10 @@
         <v>2673.5</v>
       </c>
       <c r="I57" t="n">
-        <v>3184.6</v>
+        <v>2103.6</v>
       </c>
       <c r="J57" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K57" t="n">
         <v>160883.5</v>
@@ -7073,10 +6831,10 @@
         <v>2673.5</v>
       </c>
       <c r="I58" t="n">
-        <v>3184.6</v>
+        <v>2103.6</v>
       </c>
       <c r="J58" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K58" t="n">
         <v>161854.8</v>
@@ -7126,10 +6884,10 @@
         <v>2679.5</v>
       </c>
       <c r="I59" t="n">
-        <v>3184.7</v>
+        <v>2103.7</v>
       </c>
       <c r="J59" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K59" t="n">
         <v>162463.1</v>
@@ -7179,10 +6937,10 @@
         <v>2679.5</v>
       </c>
       <c r="I60" t="n">
-        <v>3186.3</v>
+        <v>2105.3</v>
       </c>
       <c r="J60" t="n">
-        <v>1984.9</v>
+        <v>3065.9</v>
       </c>
       <c r="K60" t="n">
         <v>163115.8</v>
@@ -7232,10 +6990,10 @@
         <v>2679.5</v>
       </c>
       <c r="I61" t="n">
-        <v>3186.5</v>
+        <v>2105.3</v>
       </c>
       <c r="J61" t="n">
-        <v>1989.6</v>
+        <v>3070.9</v>
       </c>
       <c r="K61" t="n">
         <v>163850</v>
@@ -7285,10 +7043,10 @@
         <v>2679.5</v>
       </c>
       <c r="I62" t="n">
-        <v>3197.7</v>
+        <v>2111.7</v>
       </c>
       <c r="J62" t="n">
-        <v>1989.6</v>
+        <v>3075.6</v>
       </c>
       <c r="K62" t="n">
         <v>164544</v>
@@ -7338,10 +7096,10 @@
         <v>2679.5</v>
       </c>
       <c r="I63" t="n">
-        <v>3197.7</v>
+        <v>2111.7</v>
       </c>
       <c r="J63" t="n">
-        <v>1989.6</v>
+        <v>3075.6</v>
       </c>
       <c r="K63" t="n">
         <v>165060.8</v>
@@ -7391,10 +7149,10 @@
         <v>2679.5</v>
       </c>
       <c r="I64" t="n">
-        <v>3198.6</v>
+        <v>2112.6</v>
       </c>
       <c r="J64" t="n">
-        <v>1989.6</v>
+        <v>3075.6</v>
       </c>
       <c r="K64" t="n">
         <v>165921.2</v>
@@ -7444,10 +7202,10 @@
         <v>2679.5</v>
       </c>
       <c r="I65" t="n">
-        <v>3203.4</v>
+        <v>2112.7</v>
       </c>
       <c r="J65" t="n">
-        <v>1990.5</v>
+        <v>3081.3</v>
       </c>
       <c r="K65" t="n">
         <v>166588.5</v>
@@ -7497,10 +7255,10 @@
         <v>2679.5</v>
       </c>
       <c r="I66" t="n">
-        <v>3203.9</v>
+        <v>2113.2</v>
       </c>
       <c r="J66" t="n">
-        <v>1990.5</v>
+        <v>3081.3</v>
       </c>
       <c r="K66" t="n">
         <v>167376</v>
@@ -7550,10 +7308,10 @@
         <v>2679.5</v>
       </c>
       <c r="I67" t="n">
-        <v>3206.7</v>
+        <v>2113.2</v>
       </c>
       <c r="J67" t="n">
-        <v>1990.5</v>
+        <v>3084.1</v>
       </c>
       <c r="K67" t="n">
         <v>167880</v>
@@ -7603,10 +7361,10 @@
         <v>2679.5</v>
       </c>
       <c r="I68" t="n">
-        <v>3206.8</v>
+        <v>2113.2</v>
       </c>
       <c r="J68" t="n">
-        <v>1990.5</v>
+        <v>3084.1</v>
       </c>
       <c r="K68" t="n">
         <v>168418</v>
@@ -7656,10 +7414,10 @@
         <v>2679.5</v>
       </c>
       <c r="I69" t="n">
-        <v>3206.8</v>
+        <v>2113.2</v>
       </c>
       <c r="J69" t="n">
-        <v>1990.5</v>
+        <v>3084.1</v>
       </c>
       <c r="K69" t="n">
         <v>169117.2</v>
@@ -7893,16 +7651,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2882.2</v>
+        <v>1888</v>
       </c>
       <c r="D9" t="n">
         <v>1579</v>
       </c>
       <c r="E9" t="n">
-        <v>1303.2</v>
+        <v>309</v>
       </c>
       <c r="F9" t="n">
-        <v>82.5</v>
+        <v>19.6</v>
       </c>
     </row>
     <row r="10">
@@ -7915,16 +7673,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1833.7</v>
+        <v>2827.9</v>
       </c>
       <c r="D10" t="n">
         <v>1826</v>
       </c>
       <c r="E10" t="n">
-        <v>7.7</v>
+        <v>1001.9</v>
       </c>
       <c r="F10" t="n">
-        <v>0.4</v>
+        <v>54.9</v>
       </c>
     </row>
     <row r="11">
@@ -8113,16 +7871,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3017.5</v>
+        <v>1997.2</v>
       </c>
       <c r="D19" t="n">
         <v>1301</v>
       </c>
       <c r="E19" t="n">
-        <v>1716.5</v>
+        <v>696.2</v>
       </c>
       <c r="F19" t="n">
-        <v>131.9</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="20">
@@ -8135,16 +7893,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="D20" t="n">
         <v>2349</v>
       </c>
       <c r="E20" t="n">
-        <v>-514.8</v>
+        <v>505.6</v>
       </c>
       <c r="F20" t="n">
-        <v>-21.9</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="21">
@@ -8333,16 +8091,16 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3078.6</v>
+        <v>2044.9</v>
       </c>
       <c r="D29" t="n">
         <v>1343</v>
       </c>
       <c r="E29" t="n">
-        <v>1735.6</v>
+        <v>701.9</v>
       </c>
       <c r="F29" t="n">
-        <v>129.2</v>
+        <v>52.3</v>
       </c>
     </row>
     <row r="30">
@@ -8355,16 +8113,16 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1882.6</v>
+        <v>2916.3</v>
       </c>
       <c r="D30" t="n">
         <v>2319</v>
       </c>
       <c r="E30" t="n">
-        <v>-436.4</v>
+        <v>597.3</v>
       </c>
       <c r="F30" t="n">
-        <v>-18.8</v>
+        <v>25.8</v>
       </c>
     </row>
     <row r="31">
@@ -8553,16 +8311,16 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3132</v>
+        <v>2071.3</v>
       </c>
       <c r="D39" t="n">
         <v>1408</v>
       </c>
       <c r="E39" t="n">
-        <v>1724</v>
+        <v>663.3</v>
       </c>
       <c r="F39" t="n">
-        <v>122.4</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="40">
@@ -8575,16 +8333,16 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1894.3</v>
+        <v>2955</v>
       </c>
       <c r="D40" t="n">
         <v>2081</v>
       </c>
       <c r="E40" t="n">
-        <v>-186.7</v>
+        <v>874</v>
       </c>
       <c r="F40" t="n">
-        <v>-9</v>
+        <v>42</v>
       </c>
     </row>
     <row r="41">
@@ -8773,16 +8531,16 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>3160.2</v>
+        <v>2080.1</v>
       </c>
       <c r="D49" t="n">
         <v>1413</v>
       </c>
       <c r="E49" t="n">
-        <v>1747.2</v>
+        <v>667.1</v>
       </c>
       <c r="F49" t="n">
-        <v>123.7</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="50">
@@ -8795,16 +8553,16 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>1960.9</v>
+        <v>3041.1</v>
       </c>
       <c r="D50" t="n">
         <v>2331</v>
       </c>
       <c r="E50" t="n">
-        <v>-370.1</v>
+        <v>710.1</v>
       </c>
       <c r="F50" t="n">
-        <v>-15.9</v>
+        <v>30.5</v>
       </c>
     </row>
     <row r="51">
@@ -8993,16 +8751,16 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3197.7</v>
+        <v>2111.7</v>
       </c>
       <c r="D59" t="n">
         <v>1435</v>
       </c>
       <c r="E59" t="n">
-        <v>1762.7</v>
+        <v>676.7</v>
       </c>
       <c r="F59" t="n">
-        <v>122.8</v>
+        <v>47.2</v>
       </c>
     </row>
     <row r="60">
@@ -9015,16 +8773,16 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>1989.6</v>
+        <v>3075.6</v>
       </c>
       <c r="D60" t="n">
         <v>2534</v>
       </c>
       <c r="E60" t="n">
-        <v>-544.4</v>
+        <v>541.6</v>
       </c>
       <c r="F60" t="n">
-        <v>-21.5</v>
+        <v>21.4</v>
       </c>
     </row>
     <row r="61">
@@ -9326,16 +9084,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2882.2</v>
+        <v>1888</v>
       </c>
       <c r="D10" t="n">
         <v>2233</v>
       </c>
       <c r="E10" t="n">
-        <v>649.2</v>
+        <v>-345</v>
       </c>
       <c r="F10" t="n">
-        <v>29.1</v>
+        <v>-15.5</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -9380,16 +9138,16 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1833.7</v>
+        <v>2827.9</v>
       </c>
       <c r="D12" t="n">
         <v>2326.4</v>
       </c>
       <c r="E12" t="n">
-        <v>-492.7</v>
+        <v>501.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-21.2</v>
+        <v>21.6</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -9623,16 +9381,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3017.5</v>
+        <v>1997.2</v>
       </c>
       <c r="D21" t="n">
         <v>2471</v>
       </c>
       <c r="E21" t="n">
-        <v>546.5</v>
+        <v>-473.8</v>
       </c>
       <c r="F21" t="n">
-        <v>22.1</v>
+        <v>-19.2</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -9677,16 +9435,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1834.2</v>
+        <v>2854.6</v>
       </c>
       <c r="D23" t="n">
         <v>2352.6</v>
       </c>
       <c r="E23" t="n">
-        <v>-518.4</v>
+        <v>502</v>
       </c>
       <c r="F23" t="n">
-        <v>-22</v>
+        <v>21.3</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -9920,16 +9678,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3078.6</v>
+        <v>2044.9</v>
       </c>
       <c r="D32" t="n">
         <v>2550.1</v>
       </c>
       <c r="E32" t="n">
-        <v>528.5</v>
+        <v>-505.2</v>
       </c>
       <c r="F32" t="n">
-        <v>20.7</v>
+        <v>-19.8</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -9974,16 +9732,16 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1882.6</v>
+        <v>2916.3</v>
       </c>
       <c r="D34" t="n">
         <v>2338.9</v>
       </c>
       <c r="E34" t="n">
-        <v>-456.3</v>
+        <v>577.4</v>
       </c>
       <c r="F34" t="n">
-        <v>-19.5</v>
+        <v>24.7</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -10217,16 +9975,16 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3132</v>
+        <v>2071.3</v>
       </c>
       <c r="D43" t="n">
         <v>2715</v>
       </c>
       <c r="E43" t="n">
-        <v>417</v>
+        <v>-643.7</v>
       </c>
       <c r="F43" t="n">
-        <v>15.4</v>
+        <v>-23.7</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -10271,16 +10029,16 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1894.3</v>
+        <v>2955</v>
       </c>
       <c r="D45" t="n">
         <v>378.3</v>
       </c>
       <c r="E45" t="n">
-        <v>1516</v>
+        <v>2576.7</v>
       </c>
       <c r="F45" t="n">
-        <v>400.7</v>
+        <v>681.1</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -10514,16 +10272,16 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3160.2</v>
+        <v>2080.1</v>
       </c>
       <c r="D54" t="n">
         <v>3106.7</v>
       </c>
       <c r="E54" t="n">
-        <v>53.5</v>
+        <v>-1026.6</v>
       </c>
       <c r="F54" t="n">
-        <v>1.7</v>
+        <v>-33</v>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -10568,16 +10326,16 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>1960.9</v>
+        <v>3041.1</v>
       </c>
       <c r="D56" t="n">
         <v>389.5</v>
       </c>
       <c r="E56" t="n">
-        <v>1571.4</v>
+        <v>2651.6</v>
       </c>
       <c r="F56" t="n">
-        <v>403.4</v>
+        <v>680.7</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -10811,16 +10569,16 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3197.7</v>
+        <v>2111.7</v>
       </c>
       <c r="D65" t="n">
         <v>3194.1</v>
       </c>
       <c r="E65" t="n">
-        <v>3.6</v>
+        <v>-1082.4</v>
       </c>
       <c r="F65" t="n">
-        <v>0.1</v>
+        <v>-33.9</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -10865,16 +10623,16 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>1989.6</v>
+        <v>3075.6</v>
       </c>
       <c r="D67" t="n">
         <v>534.9</v>
       </c>
       <c r="E67" t="n">
-        <v>1454.7</v>
+        <v>2540.7</v>
       </c>
       <c r="F67" t="n">
-        <v>272</v>
+        <v>475</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -11108,10 +10866,10 @@
         </is>
       </c>
       <c r="C76" t="n">
-        <v>3206.8</v>
+        <v>2113.2</v>
       </c>
       <c r="D76" t="n">
-        <v>3206.8</v>
+        <v>2113.2</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -11162,10 +10920,10 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>1990.5</v>
+        <v>3084.1</v>
       </c>
       <c r="D78" t="n">
-        <v>1990.5</v>
+        <v>3084.1</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -14174,13 +13932,13 @@
         <v>2679.4974</v>
       </c>
       <c r="K8" t="n">
-        <v>3206.78939</v>
+        <v>2113.21104</v>
       </c>
       <c r="L8" t="n">
         <v>2265.333</v>
       </c>
       <c r="M8" t="n">
-        <v>1990.51434</v>
+        <v>3084.09269</v>
       </c>
       <c r="N8" t="n">
         <v>6152.184298</v>

--- a/output/Data and Chart Outputs/france_power_capacity_monthly.xlsx
+++ b/output/Data and Chart Outputs/france_power_capacity_monthly.xlsx
@@ -1105,17 +1105,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-12 04:52 UTC</t>
+          <t>2026-10-12 04:54 UTC</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Registre national des installations de production et de stockage d'électricité (au 31/07/2026); processed 2026-09-10T14:01:40+00:00; rules v2</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>03dc155484b2e99c0cb61ae23b596bf0c965139dc49f7730164d93a649a18e22</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1122,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-10-12 04:52 UTC</t>
+          <t>2026-10-12 04:54 UTC</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
